--- a/Phan_Cong.xlsx
+++ b/Phan_Cong.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SCHOOL\Hk2_nam_3\Quan_Tri_Du_An_CNTT\btth9\NguyenTuanAnh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4AF2E6-2C4A-4F5A-8099-F8741B6F6FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDB1019-061D-4987-9E0F-08DB7EF1E18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{38B4B71A-B216-4752-AB30-749D8880233C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{38B4B71A-B216-4752-AB30-749D8880233C}"/>
   </bookViews>
   <sheets>
     <sheet name="Bang_Thanh_Vien" sheetId="1" r:id="rId1"/>
-    <sheet name="Bang_Cong_Viec" sheetId="2" r:id="rId2"/>
+    <sheet name="Gioi_thieu_Du_An" sheetId="2" r:id="rId2"/>
+    <sheet name="Phan_Cong" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>Danh sách thành viên tham gia làm dự án</t>
   </si>
@@ -66,17 +67,170 @@
     <t>Thành viên</t>
   </si>
   <si>
-    <t xml:space="preserve">Danh sách công việc </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>Tên dự án</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công nghệ sử dụng </t>
+  </si>
+  <si>
+    <t>Mục đích</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mục tiêu </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hệ thống quản trị dự án CNTT</t>
+  </si>
+  <si>
+    <t>ReactJS + FastAPI + PostgreSQL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xây dựng hệ thống website quản lý CNTT giúp các đội nhóm dự án dễ dàng lập kế hoạch, theo dõi tiến độ, kiểm tra chặt chẽ thời gian, chi phí một cách hiệu quả. </t>
+  </si>
+  <si>
+    <t>Hoàn thành thiết kế, lập trình và triển khai dự án ổn định.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỗ trợ phân quyền Trưởng dự án và Đội dự án. Quản lý truy cập thông qua mã dự án. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàn thiện các chức năng cốt lõi: </t>
+  </si>
+  <si>
+    <t>1.Quản lý công việc</t>
+  </si>
+  <si>
+    <t>2.Ước lượng thời gian công việc (Expert)</t>
+  </si>
+  <si>
+    <t>3.Ước lượng chi phí cho dự án</t>
+  </si>
+  <si>
+    <t>4.Quản lý lịch trình dự án</t>
+  </si>
+  <si>
+    <t>5.Quản lý lịch trình công việc cho dự án</t>
+  </si>
+  <si>
+    <t>Nộp đẩy đủ tài liệu (Source code cập nhật theo buổi, file phân công nhiệm vụ, file những việc đã làm trong buổi thực hành)</t>
+  </si>
+  <si>
+    <t>Mã CV</t>
+  </si>
+  <si>
+    <t>Khởi tạo &amp; Phân quyền (Login)</t>
+  </si>
+  <si>
+    <t>Setup base project</t>
+  </si>
+  <si>
+    <t>Tạo dự án Vite + React + Tailwind</t>
+  </si>
+  <si>
+    <t>Khởi tạo FastAPI + SQLAlchemy</t>
+  </si>
+  <si>
+    <t>Thiết kế Database</t>
+  </si>
+  <si>
+    <t>(Phối hợp chốt schema JSON)</t>
+  </si>
+  <si>
+    <t>Thiết kế 4 bảng (Users, Projects, Tasks...)</t>
+  </si>
+  <si>
+    <t>Chức năng Đăng nhập &amp; Auth</t>
+  </si>
+  <si>
+    <t>Dựng Form Login, lưu Token (Local Storage)</t>
+  </si>
+  <si>
+    <t>Code API Login, tạo &amp; mã hóa JWT</t>
+  </si>
+  <si>
+    <t>Join dự án bằng Mã (Project Code)</t>
+  </si>
+  <si>
+    <t>Dựng Form nhập mã, gọi API join dự án</t>
+  </si>
+  <si>
+    <t>Code API kiểm tra mã &amp; phân quyền</t>
+  </si>
+  <si>
+    <t>Giao diện Bảng công việc (WBS)</t>
+  </si>
+  <si>
+    <t>Dùng AntD/MUI dựng Table hiển thị dạng Cha-Con</t>
+  </si>
+  <si>
+    <t>API CRUD (Thêm/Sửa/Xóa/Lấy) cho bảng Tasks</t>
+  </si>
+  <si>
+    <t>Tính toán PERT (Thời gian)</t>
+  </si>
+  <si>
+    <t>Làm Form nhập 3 số MO, ML, MP</t>
+  </si>
+  <si>
+    <t>Viết logic tính EST, cập nhật vào DB</t>
+  </si>
+  <si>
+    <t>Quản lý Chi phí</t>
+  </si>
+  <si>
+    <t>Thêm cột nhập Tiền vào bảng Table</t>
+  </si>
+  <si>
+    <t>Cập nhật API Tasks để nhận &amp; lưu biến số Tiền</t>
+  </si>
+  <si>
+    <t>Trực quan hóa (Kanban &amp; Gantt)</t>
+  </si>
+  <si>
+    <t>Bảng Kanban (Kéo thả thẻ)</t>
+  </si>
+  <si>
+    <t>Tích hợp thư viện (dnd-kit), code giao diện kéo thả</t>
+  </si>
+  <si>
+    <t>API Update Status (/tasks/{id}/status)</t>
+  </si>
+  <si>
+    <t>Biểu đồ Gantt</t>
+  </si>
+  <si>
+    <t>Tích hợp thư viện Gantt, map data ngày tháng</t>
+  </si>
+  <si>
+    <t>(Đã có data từ API Tasks, hỗ trợ test)</t>
+  </si>
+  <si>
+    <t>Tổng duyệt &amp; Báo cáo</t>
+  </si>
+  <si>
+    <t>Viết file báo cáo UI/UX, hướng dẫn sử dụng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Frontend (Tuấn Anh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Backend (Vũ)</t>
+  </si>
+  <si>
+    <t>Hạng mục công việc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quản lý WBS &amp; PERT </t>
+  </si>
+  <si>
+    <t>Khởi chạy test Postman hoặc Swagger UI, fix bug logic API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +260,56 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -127,7 +331,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -264,14 +468,142 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -281,38 +613,87 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,53 +1038,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="9">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>23050118</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="13">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>23050102</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -723,18 +1104,416 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9D5286-D0A4-4B83-83AE-C4FC632A9FE3}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:19" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+    </row>
+    <row r="4" spans="1:19" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="26"/>
+      <c r="B5" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="26"/>
+      <c r="B6" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+    </row>
+    <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+    </row>
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+    </row>
+    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:19" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="A4:A12"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D631DB77-8D3F-4640-BBBB-D5BF95C6B06C}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" customWidth="1"/>
+    <col min="4" max="4" width="45.21875" customWidth="1"/>
+    <col min="5" max="5" width="27.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A1" s="30" t="str">
+        <f>UPPER("Danh sách công việc cần lầm")</f>
+        <v>DANH SÁCH CÔNG VIỆC CẦN LẦM</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="2" spans="1:5" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="41">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="33"/>
+    </row>
+    <row r="5" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="33"/>
+    </row>
+    <row r="6" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="34">
+        <v>1.3</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="33"/>
+    </row>
+    <row r="7" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="35">
+        <v>1.4</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="37"/>
+    </row>
+    <row r="8" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="41">
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="44"/>
+    </row>
+    <row r="9" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34">
+        <v>2.1</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="33"/>
+    </row>
+    <row r="10" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="34">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="33"/>
+    </row>
+    <row r="11" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="35">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="41">
+        <v>3</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34">
+        <v>3.1</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="33"/>
+    </row>
+    <row r="14" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="34">
+        <v>3.2</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="33"/>
+    </row>
+    <row r="15" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="35">
+        <v>3.3</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Phan_Cong.xlsx
+++ b/Phan_Cong.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SCHOOL\Hk2_nam_3\Quan_Tri_Du_An_CNTT\btth9\NguyenTuanAnh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDB1019-061D-4987-9E0F-08DB7EF1E18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53FCD0C-20F5-4A7A-8B6B-945107BA1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{38B4B71A-B216-4752-AB30-749D8880233C}"/>
   </bookViews>

--- a/Phan_Cong.xlsx
+++ b/Phan_Cong.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SCHOOL\Hk2_nam_3\Quan_Tri_Du_An_CNTT\btth9\NguyenTuanAnh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SCHOOL\Hk2_nam_3\Quan_Tri_Du_An_CNTT\BT_GK\NguyenTuanAnh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53FCD0C-20F5-4A7A-8B6B-945107BA1770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FA2A1E-E404-41B7-942D-EDF691EB2F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{38B4B71A-B216-4752-AB30-749D8880233C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{38B4B71A-B216-4752-AB30-749D8880233C}"/>
   </bookViews>
   <sheets>
     <sheet name="Bang_Thanh_Vien" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t>Giao diện Bảng công việc (WBS)</t>
   </si>
   <si>
-    <t>Dùng AntD/MUI dựng Table hiển thị dạng Cha-Con</t>
-  </si>
-  <si>
     <t>API CRUD (Thêm/Sửa/Xóa/Lấy) cho bảng Tasks</t>
   </si>
   <si>
@@ -224,6 +221,9 @@
   </si>
   <si>
     <t>Khởi chạy test Postman hoặc Swagger UI, fix bug logic API</t>
+  </si>
+  <si>
+    <t>Dùng AntD dựng Table hiển thị dạng Cha-Con</t>
   </si>
 </sst>
 </file>
@@ -604,6 +604,64 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -613,87 +671,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1038,12 +1038,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="36"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
@@ -1111,159 +1111,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-    </row>
-    <row r="2" spans="1:19" ht="36" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="1:19" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
     </row>
     <row r="3" spans="1:19" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
     </row>
     <row r="4" spans="1:19" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="26"/>
-      <c r="B5" s="23" t="s">
+      <c r="A5" s="39"/>
+      <c r="B5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="26"/>
-      <c r="B6" s="24" t="s">
+      <c r="A6" s="39"/>
+      <c r="B6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
     </row>
     <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="39"/>
+      <c r="B7" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="39"/>
+      <c r="B8" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="39"/>
+      <c r="B9" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28" t="s">
+      <c r="A10" s="39"/>
+      <c r="B10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="39"/>
+      <c r="B11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
     </row>
     <row r="12" spans="1:19" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="A4:A12"/>
     <mergeCell ref="B8:G8"/>
@@ -1273,10 +1277,6 @@
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1295,220 +1295,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="30" t="str">
+      <c r="A1" s="31" t="str">
         <f>UPPER("Danh sách công việc cần lầm")</f>
         <v>DANH SÁCH CÔNG VIỆC CẦN LẦM</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="21">
+        <v>1.4</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <v>2</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="41">
-        <v>1</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-    </row>
-    <row r="4" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="33"/>
-    </row>
-    <row r="5" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34">
-        <v>1.2</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="33"/>
-    </row>
-    <row r="6" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34">
-        <v>1.3</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="33"/>
-    </row>
-    <row r="7" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="35">
-        <v>1.4</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="37"/>
-    </row>
-    <row r="8" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41">
-        <v>2</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
+    </row>
+    <row r="9" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>2.1</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>3</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="30"/>
+    </row>
+    <row r="13" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="20">
+        <v>3.1</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
+        <v>3.3</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="44"/>
-    </row>
-    <row r="9" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34">
-        <v>2.1</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="33"/>
-    </row>
-    <row r="11" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="35">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="41">
-        <v>3</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="44"/>
-    </row>
-    <row r="13" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34">
-        <v>3.1</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="33"/>
-    </row>
-    <row r="14" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34">
-        <v>3.2</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="33"/>
-    </row>
-    <row r="15" spans="1:5" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="35">
-        <v>3.3</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
+      <c r="A16" s="14"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
+      <c r="A17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
